--- a/mock_backend_service/inputs/testcases.xlsx
+++ b/mock_backend_service/inputs/testcases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29311"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_91532D1D1D2052E07BCCF038A5A9E5A8F2F1C208" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{472DA7D7-99EE-4F41-ACFC-95A116400A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
     <t>/pet</t>
   </si>
   <si>
-    <t>```json
+    <t xml:space="preserve">
 {
 "method": "POST",
 "url": "https://petstore.swagger.io/v2/pet",
@@ -150,8 +150,7 @@
 ],
 "status": "available"
 }
-}
-```</t>
+}</t>
   </si>
   <si>
     <t>AddPet_002: Add a new pet with missing required fields</t>
@@ -1391,7 +1390,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="409.6">
+    <row r="2" spans="1:8" ht="396.75">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
